--- a/data/trans_orig/P1404-Clase-trans_orig.xlsx
+++ b/data/trans_orig/P1404-Clase-trans_orig.xlsx
@@ -538,7 +538,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con diagnóstico de colesterol alto en 2007</t>
+          <t>Población con diagnóstico de colesterol alto en 2007 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>21658</t>
+          <t>21519</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>41948</t>
+          <t>43171</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>4,57%</t>
+          <t>4,54%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>8,85%</t>
+          <t>9,11%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>12956</t>
+          <t>14498</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>31788</t>
+          <t>31931</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>4,22%</t>
+          <t>4,73%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>10,37%</t>
+          <t>10,41%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>39210</t>
+          <t>38887</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>68018</t>
+          <t>68372</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>5,02%</t>
+          <t>4,98%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>8,72%</t>
+          <t>8,76%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>431828</t>
+          <t>430605</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>452118</t>
+          <t>452257</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>91,15%</t>
+          <t>90,89%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>95,43%</t>
+          <t>95,46%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>274892</t>
+          <t>274749</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>293724</t>
+          <t>292182</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>89,63%</t>
+          <t>89,59%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>95,78%</t>
+          <t>95,27%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>712439</t>
+          <t>712085</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>741247</t>
+          <t>741570</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>91,28%</t>
+          <t>91,24%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>94,98%</t>
+          <t>95,02%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>21100</t>
+          <t>20331</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>42925</t>
+          <t>41354</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>5,75%</t>
+          <t>5,54%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>11,7%</t>
+          <t>11,27%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>15120</t>
+          <t>15218</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>33153</t>
+          <t>34004</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>4,07%</t>
+          <t>4,09%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>8,92%</t>
+          <t>9,14%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>40878</t>
+          <t>40091</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>68945</t>
+          <t>68264</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>5,53%</t>
+          <t>5,43%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>9,33%</t>
+          <t>9,24%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>324009</t>
+          <t>325580</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>345834</t>
+          <t>346603</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>88,3%</t>
+          <t>88,73%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>94,25%</t>
+          <t>94,46%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>338712</t>
+          <t>337861</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>356745</t>
+          <t>356647</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>91,08%</t>
+          <t>90,86%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>95,93%</t>
+          <t>95,91%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>669854</t>
+          <t>670535</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>697921</t>
+          <t>698708</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>90,67%</t>
+          <t>90,76%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>94,47%</t>
+          <t>94,57%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>44202</t>
+          <t>43571</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>73211</t>
+          <t>71389</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>8,15%</t>
+          <t>8,03%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>13,5%</t>
+          <t>13,16%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>9161</t>
+          <t>9333</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>24210</t>
+          <t>24408</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>5,46%</t>
+          <t>5,56%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>14,43%</t>
+          <t>14,55%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>57765</t>
+          <t>56606</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>87875</t>
+          <t>87630</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>8,13%</t>
+          <t>7,97%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>12,37%</t>
+          <t>12,34%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>469178</t>
+          <t>471000</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>498187</t>
+          <t>498818</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>86,5%</t>
+          <t>86,84%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>91,85%</t>
+          <t>91,97%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>143572</t>
+          <t>143374</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>158621</t>
+          <t>158449</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>85,57%</t>
+          <t>85,45%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>94,54%</t>
+          <t>94,44%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>622296</t>
+          <t>622541</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>652406</t>
+          <t>653565</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>87,63%</t>
+          <t>87,66%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>91,87%</t>
+          <t>92,03%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>93357</t>
+          <t>93535</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>134535</t>
+          <t>133668</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>7,54%</t>
+          <t>7,55%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>10,86%</t>
+          <t>10,79%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>42064</t>
+          <t>42528</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>70022</t>
+          <t>69682</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>5,89%</t>
+          <t>5,95%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>9,8%</t>
+          <t>9,76%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>144322</t>
+          <t>145430</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>191256</t>
+          <t>192362</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>7,39%</t>
+          <t>7,45%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>9,79%</t>
+          <t>9,85%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>1103799</t>
+          <t>1104666</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>1144977</t>
+          <t>1144799</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>89,14%</t>
+          <t>89,21%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>92,46%</t>
+          <t>92,45%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>644263</t>
+          <t>644603</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>672221</t>
+          <t>671757</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>90,2%</t>
+          <t>90,24%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>94,11%</t>
+          <t>94,05%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1761364</t>
+          <t>1760258</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1808298</t>
+          <t>1807190</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>90,21%</t>
+          <t>90,15%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>92,61%</t>
+          <t>92,55%</t>
         </is>
       </c>
     </row>
@@ -2105,12 +2105,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>17794</t>
+          <t>18570</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>36547</t>
+          <t>37350</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2120,12 +2120,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>5,08%</t>
+          <t>5,3%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>10,43%</t>
+          <t>10,65%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>48494</t>
+          <t>47077</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>80344</t>
+          <t>79137</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2155,12 +2155,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>8,53%</t>
+          <t>8,28%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>14,13%</t>
+          <t>13,91%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>70255</t>
+          <t>68856</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>108997</t>
+          <t>105859</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>7,64%</t>
+          <t>7,49%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>11,86%</t>
+          <t>11,52%</t>
         </is>
       </c>
     </row>
@@ -2218,12 +2218,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>314008</t>
+          <t>313205</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>332761</t>
+          <t>331985</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>89,57%</t>
+          <t>89,35%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>94,92%</t>
+          <t>94,7%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2253,12 +2253,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>488408</t>
+          <t>489615</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>520258</t>
+          <t>521675</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2268,12 +2268,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>85,87%</t>
+          <t>86,09%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>91,47%</t>
+          <t>91,72%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>810310</t>
+          <t>813448</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>849052</t>
+          <t>850451</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>88,14%</t>
+          <t>88,48%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>92,36%</t>
+          <t>92,51%</t>
         </is>
       </c>
     </row>
@@ -2453,7 +2453,7 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>7878</t>
+          <t>8109</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2468,7 +2468,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>2,64%</t>
+          <t>2,72%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2483,12 +2483,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>147041</t>
+          <t>146871</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>194357</t>
+          <t>196715</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2498,12 +2498,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>11,77%</t>
+          <t>11,76%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>15,56%</t>
+          <t>15,75%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2518,12 +2518,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>149768</t>
+          <t>150861</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>198545</t>
+          <t>201932</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2533,12 +2533,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>9,68%</t>
+          <t>9,75%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>12,83%</t>
+          <t>13,05%</t>
         </is>
       </c>
     </row>
@@ -2561,7 +2561,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>290323</t>
+          <t>290092</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -2576,7 +2576,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>97,36%</t>
+          <t>97,28%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -2596,12 +2596,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>1054403</t>
+          <t>1052045</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>1101719</t>
+          <t>1101889</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2611,12 +2611,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>84,44%</t>
+          <t>84,25%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>88,23%</t>
+          <t>88,24%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2631,12 +2631,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>1348415</t>
+          <t>1345028</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>1397192</t>
+          <t>1396099</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2646,12 +2646,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>87,17%</t>
+          <t>86,95%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>90,32%</t>
+          <t>90,25%</t>
         </is>
       </c>
     </row>
@@ -2791,12 +2791,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>226294</t>
+          <t>229426</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>286764</t>
+          <t>290099</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2806,12 +2806,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>6,92%</t>
+          <t>7,02%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>8,77%</t>
+          <t>8,87%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2826,12 +2826,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>312580</t>
+          <t>313868</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>387099</t>
+          <t>386536</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2841,12 +2841,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>9,25%</t>
+          <t>9,29%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>11,46%</t>
+          <t>11,44%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>563990</t>
+          <t>559925</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>657827</t>
+          <t>659148</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2876,12 +2876,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>8,48%</t>
+          <t>8,42%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>9,89%</t>
+          <t>9,91%</t>
         </is>
       </c>
     </row>
@@ -2904,12 +2904,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>2983426</t>
+          <t>2980091</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>3043896</t>
+          <t>3040764</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>91,23%</t>
+          <t>91,13%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>93,08%</t>
+          <t>92,98%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2939,12 +2939,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>2991025</t>
+          <t>2991588</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>3065544</t>
+          <t>3064256</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2954,12 +2954,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>88,54%</t>
+          <t>88,56%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>90,75%</t>
+          <t>90,71%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2974,12 +2974,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>5990487</t>
+          <t>5989166</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>6084324</t>
+          <t>6088389</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2989,12 +2989,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>90,11%</t>
+          <t>90,09%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>91,52%</t>
+          <t>91,58%</t>
         </is>
       </c>
     </row>
@@ -3173,7 +3173,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con diagnóstico de colesterol alto en 2012</t>
+          <t>Población con diagnóstico de colesterol alto en 2012 (tasa de respuesta: 99,95%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -3368,12 +3368,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>29352</t>
+          <t>28945</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>56518</t>
+          <t>55838</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3383,12 +3383,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>6,71%</t>
+          <t>6,62%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>12,93%</t>
+          <t>12,77%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3403,12 +3403,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>12235</t>
+          <t>12221</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>30917</t>
+          <t>30914</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3438,12 +3438,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>46924</t>
+          <t>46315</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>80515</t>
+          <t>78769</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3453,12 +3453,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>6,24%</t>
+          <t>6,16%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>10,71%</t>
+          <t>10,48%</t>
         </is>
       </c>
     </row>
@@ -3481,12 +3481,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>380693</t>
+          <t>381373</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>407859</t>
+          <t>408266</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -3496,12 +3496,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>87,07%</t>
+          <t>87,23%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>93,29%</t>
+          <t>93,38%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -3516,12 +3516,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>283537</t>
+          <t>283540</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>302219</t>
+          <t>302233</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -3551,12 +3551,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>671150</t>
+          <t>672896</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>704741</t>
+          <t>705350</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3566,12 +3566,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>89,29%</t>
+          <t>89,52%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>93,76%</t>
+          <t>93,84%</t>
         </is>
       </c>
     </row>
@@ -3711,12 +3711,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>26786</t>
+          <t>26542</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>51224</t>
+          <t>51735</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -3726,12 +3726,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>6,4%</t>
+          <t>6,34%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>12,23%</t>
+          <t>12,35%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -3746,12 +3746,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>16454</t>
+          <t>16082</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>37255</t>
+          <t>35630</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -3761,12 +3761,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>4,87%</t>
+          <t>4,76%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>11,02%</t>
+          <t>10,54%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3781,12 +3781,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>47552</t>
+          <t>47920</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>78852</t>
+          <t>78997</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3796,12 +3796,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>6,28%</t>
+          <t>6,33%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>10,42%</t>
+          <t>10,44%</t>
         </is>
       </c>
     </row>
@@ -3824,12 +3824,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>367573</t>
+          <t>367062</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>392011</t>
+          <t>392255</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -3839,12 +3839,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>87,77%</t>
+          <t>87,65%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>93,6%</t>
+          <t>93,66%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -3859,12 +3859,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>300756</t>
+          <t>302381</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>321557</t>
+          <t>321929</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -3874,12 +3874,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>88,98%</t>
+          <t>89,46%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>95,13%</t>
+          <t>95,24%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3894,12 +3894,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>677956</t>
+          <t>677811</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>709256</t>
+          <t>708888</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3909,12 +3909,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>89,58%</t>
+          <t>89,56%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>93,72%</t>
+          <t>93,67%</t>
         </is>
       </c>
     </row>
@@ -4054,12 +4054,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>71384</t>
+          <t>69599</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>106753</t>
+          <t>105815</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4069,12 +4069,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>11,37%</t>
+          <t>11,08%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>17,0%</t>
+          <t>16,85%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4089,12 +4089,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>15520</t>
+          <t>14856</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>32785</t>
+          <t>33834</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4104,12 +4104,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>5,97%</t>
+          <t>5,71%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>12,6%</t>
+          <t>13,01%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4124,12 +4124,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>90039</t>
+          <t>89903</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>130603</t>
+          <t>130162</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4139,12 +4139,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>10,14%</t>
+          <t>10,12%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>14,71%</t>
+          <t>14,66%</t>
         </is>
       </c>
     </row>
@@ -4167,12 +4167,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>521253</t>
+          <t>522191</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>556622</t>
+          <t>558407</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4182,12 +4182,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>83,0%</t>
+          <t>83,15%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>88,63%</t>
+          <t>88,92%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4202,12 +4202,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>227344</t>
+          <t>226295</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>244609</t>
+          <t>245273</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4217,12 +4217,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>87,4%</t>
+          <t>86,99%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>94,03%</t>
+          <t>94,29%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4237,12 +4237,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>757533</t>
+          <t>757974</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>798097</t>
+          <t>798233</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4252,12 +4252,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>85,29%</t>
+          <t>85,34%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>89,86%</t>
+          <t>89,88%</t>
         </is>
       </c>
     </row>
@@ -4397,12 +4397,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>132249</t>
+          <t>131885</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>181959</t>
+          <t>178574</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4412,12 +4412,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>11,41%</t>
+          <t>11,38%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>15,7%</t>
+          <t>15,41%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -4432,12 +4432,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>57603</t>
+          <t>54725</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>91995</t>
+          <t>88817</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -4447,12 +4447,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>7,53%</t>
+          <t>7,16%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>12,03%</t>
+          <t>11,61%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -4467,12 +4467,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>198209</t>
+          <t>199080</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>260875</t>
+          <t>255995</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4482,12 +4482,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>10,3%</t>
+          <t>10,35%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>13,56%</t>
+          <t>13,31%</t>
         </is>
       </c>
     </row>
@@ -4510,12 +4510,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>977050</t>
+          <t>980435</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>1026760</t>
+          <t>1027124</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4525,12 +4525,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>84,3%</t>
+          <t>84,59%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>88,59%</t>
+          <t>88,62%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -4545,12 +4545,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>672727</t>
+          <t>675905</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>707119</t>
+          <t>709997</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -4560,12 +4560,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>87,97%</t>
+          <t>88,39%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>92,47%</t>
+          <t>92,84%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -4580,12 +4580,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1662856</t>
+          <t>1667736</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1725522</t>
+          <t>1724651</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4595,12 +4595,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>86,44%</t>
+          <t>86,69%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>89,7%</t>
+          <t>89,65%</t>
         </is>
       </c>
     </row>
@@ -4740,12 +4740,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>51268</t>
+          <t>51101</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>82907</t>
+          <t>81359</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4755,12 +4755,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>10,04%</t>
+          <t>10,01%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>16,24%</t>
+          <t>15,93%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4775,12 +4775,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>114094</t>
+          <t>114775</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>155952</t>
+          <t>155658</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4790,12 +4790,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>15,01%</t>
+          <t>15,1%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>20,51%</t>
+          <t>20,47%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4810,12 +4810,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>174540</t>
+          <t>170093</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>226624</t>
+          <t>224285</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4825,12 +4825,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>13,73%</t>
+          <t>13,38%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>17,83%</t>
+          <t>17,65%</t>
         </is>
       </c>
     </row>
@@ -4853,12 +4853,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>427689</t>
+          <t>429237</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>459328</t>
+          <t>459495</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4868,12 +4868,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>83,76%</t>
+          <t>84,07%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>89,96%</t>
+          <t>89,99%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4888,12 +4888,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>604294</t>
+          <t>604588</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>646152</t>
+          <t>645471</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4903,12 +4903,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>79,49%</t>
+          <t>79,53%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>84,99%</t>
+          <t>84,9%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4923,12 +4923,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1044219</t>
+          <t>1046558</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1096303</t>
+          <t>1100750</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4938,12 +4938,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>82,17%</t>
+          <t>82,35%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>86,27%</t>
+          <t>86,62%</t>
         </is>
       </c>
     </row>
@@ -5083,12 +5083,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>939</t>
+          <t>935</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>11586</t>
+          <t>11544</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5103,7 +5103,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>4,34%</t>
+          <t>4,33%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5118,12 +5118,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>188426</t>
+          <t>191314</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>242687</t>
+          <t>246106</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5133,12 +5133,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>16,99%</t>
+          <t>17,25%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>21,88%</t>
+          <t>22,18%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5153,12 +5153,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>195539</t>
+          <t>192296</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>252826</t>
+          <t>249468</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5168,12 +5168,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>14,21%</t>
+          <t>13,97%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>18,37%</t>
+          <t>18,13%</t>
         </is>
       </c>
     </row>
@@ -5196,12 +5196,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>255296</t>
+          <t>255338</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>265943</t>
+          <t>265947</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5211,7 +5211,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>95,66%</t>
+          <t>95,67%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -5231,12 +5231,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>866664</t>
+          <t>863245</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>920925</t>
+          <t>918037</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5246,12 +5246,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>78,12%</t>
+          <t>77,82%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>83,01%</t>
+          <t>82,75%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5266,12 +5266,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>1123407</t>
+          <t>1126765</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>1180694</t>
+          <t>1183937</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5281,12 +5281,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>81,63%</t>
+          <t>81,87%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>85,79%</t>
+          <t>86,03%</t>
         </is>
       </c>
     </row>
@@ -5426,12 +5426,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>347239</t>
+          <t>351597</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>429191</t>
+          <t>424285</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5441,12 +5441,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>10,15%</t>
+          <t>10,28%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>12,55%</t>
+          <t>12,4%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5461,12 +5461,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>445191</t>
+          <t>446738</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>530152</t>
+          <t>534749</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5476,12 +5476,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>12,55%</t>
+          <t>12,6%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>14,95%</t>
+          <t>15,08%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5496,12 +5496,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>818292</t>
+          <t>817685</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>938050</t>
+          <t>936645</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5516,7 +5516,7 @@
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>13,46%</t>
+          <t>13,44%</t>
         </is>
       </c>
     </row>
@@ -5539,12 +5539,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>2991310</t>
+          <t>2996216</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>3073262</t>
+          <t>3068904</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -5554,12 +5554,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>87,45%</t>
+          <t>87,6%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>89,85%</t>
+          <t>89,72%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -5574,12 +5574,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>3016763</t>
+          <t>3012166</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>3101724</t>
+          <t>3100177</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -5589,12 +5589,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>85,05%</t>
+          <t>84,92%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>87,45%</t>
+          <t>87,4%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -5609,12 +5609,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>6029366</t>
+          <t>6030771</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>6149124</t>
+          <t>6149731</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -5624,7 +5624,7 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>86,54%</t>
+          <t>86,56%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
@@ -5808,7 +5808,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con diagnóstico de colesterol alto en 2016</t>
+          <t>Población con diagnóstico de colesterol alto en 2016 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -6003,12 +6003,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>32824</t>
+          <t>33046</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>58214</t>
+          <t>58968</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -6018,12 +6018,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>7,65%</t>
+          <t>7,7%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>13,57%</t>
+          <t>13,74%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6038,12 +6038,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>18569</t>
+          <t>17946</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>40900</t>
+          <t>41615</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -6053,12 +6053,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>5,35%</t>
+          <t>5,17%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>11,78%</t>
+          <t>11,99%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6073,12 +6073,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>57672</t>
+          <t>56210</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>92498</t>
+          <t>91520</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6088,12 +6088,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>7,43%</t>
+          <t>7,24%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>11,92%</t>
+          <t>11,79%</t>
         </is>
       </c>
     </row>
@@ -6116,12 +6116,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>370878</t>
+          <t>370124</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>396268</t>
+          <t>396046</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -6131,12 +6131,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>86,43%</t>
+          <t>86,26%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>92,35%</t>
+          <t>92,3%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -6151,12 +6151,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>306155</t>
+          <t>305440</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>328486</t>
+          <t>329109</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -6166,12 +6166,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>88,22%</t>
+          <t>88,01%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>94,65%</t>
+          <t>94,83%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6186,12 +6186,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>683649</t>
+          <t>684627</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>718475</t>
+          <t>719937</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -6201,12 +6201,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>88,08%</t>
+          <t>88,21%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>92,57%</t>
+          <t>92,76%</t>
         </is>
       </c>
     </row>
@@ -6346,12 +6346,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>28406</t>
+          <t>28790</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>54589</t>
+          <t>53118</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -6361,12 +6361,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>7,53%</t>
+          <t>7,63%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>14,47%</t>
+          <t>14,08%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -6381,12 +6381,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>22395</t>
+          <t>22367</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>45463</t>
+          <t>44839</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -6396,12 +6396,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>6,02%</t>
+          <t>6,01%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>12,21%</t>
+          <t>12,04%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -6416,12 +6416,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>55551</t>
+          <t>56666</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>91176</t>
+          <t>90991</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -6431,12 +6431,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>7,41%</t>
+          <t>7,56%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>12,16%</t>
+          <t>12,14%</t>
         </is>
       </c>
     </row>
@@ -6459,12 +6459,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>322638</t>
+          <t>324109</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>348821</t>
+          <t>348437</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -6474,12 +6474,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>85,53%</t>
+          <t>85,92%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>92,47%</t>
+          <t>92,37%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -6494,12 +6494,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>326810</t>
+          <t>327434</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>349878</t>
+          <t>349906</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -6509,12 +6509,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>87,79%</t>
+          <t>87,96%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>93,98%</t>
+          <t>93,99%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -6529,12 +6529,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>658324</t>
+          <t>658509</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>693949</t>
+          <t>692834</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -6544,12 +6544,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>87,84%</t>
+          <t>87,86%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>92,59%</t>
+          <t>92,44%</t>
         </is>
       </c>
     </row>
@@ -6689,12 +6689,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>58553</t>
+          <t>58500</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>91012</t>
+          <t>89545</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -6704,12 +6704,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>11,22%</t>
+          <t>11,21%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>17,44%</t>
+          <t>17,16%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -6724,12 +6724,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>12982</t>
+          <t>14545</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>33981</t>
+          <t>33027</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -6739,12 +6739,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>7,81%</t>
+          <t>8,76%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>20,46%</t>
+          <t>19,88%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6759,12 +6759,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>76887</t>
+          <t>76877</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>115149</t>
+          <t>115129</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -6779,7 +6779,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>16,74%</t>
+          <t>16,73%</t>
         </is>
       </c>
     </row>
@@ -6802,12 +6802,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>430902</t>
+          <t>432369</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>463361</t>
+          <t>463414</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -6817,12 +6817,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>82,56%</t>
+          <t>82,84%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>88,78%</t>
+          <t>88,79%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -6837,12 +6837,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>132142</t>
+          <t>133096</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>153141</t>
+          <t>151578</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -6852,12 +6852,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>79,54%</t>
+          <t>80,12%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>92,19%</t>
+          <t>91,24%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -6872,12 +6872,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>572887</t>
+          <t>572907</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>611149</t>
+          <t>611159</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -6887,7 +6887,7 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>83,26%</t>
+          <t>83,27%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -7032,12 +7032,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>123543</t>
+          <t>124573</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>170313</t>
+          <t>168528</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -7047,12 +7047,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>10,75%</t>
+          <t>10,84%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>14,81%</t>
+          <t>14,66%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7067,12 +7067,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>62798</t>
+          <t>62047</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>95681</t>
+          <t>95201</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -7082,12 +7082,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>7,6%</t>
+          <t>7,51%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>11,59%</t>
+          <t>11,53%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7102,12 +7102,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>193711</t>
+          <t>194329</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>250512</t>
+          <t>251847</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -7117,12 +7117,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>9,81%</t>
+          <t>9,84%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>12,68%</t>
+          <t>12,75%</t>
         </is>
       </c>
     </row>
@@ -7145,12 +7145,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>979325</t>
+          <t>981110</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>1026095</t>
+          <t>1025065</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -7160,12 +7160,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>85,19%</t>
+          <t>85,34%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>89,25%</t>
+          <t>89,16%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7180,12 +7180,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>730195</t>
+          <t>730675</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>763078</t>
+          <t>763829</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -7195,12 +7195,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>88,41%</t>
+          <t>88,47%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>92,4%</t>
+          <t>92,49%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7215,12 +7215,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1725002</t>
+          <t>1723667</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1781803</t>
+          <t>1781185</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -7230,12 +7230,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>87,32%</t>
+          <t>87,25%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>90,19%</t>
+          <t>90,16%</t>
         </is>
       </c>
     </row>
@@ -7375,12 +7375,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>65282</t>
+          <t>66861</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>98512</t>
+          <t>99423</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -7390,12 +7390,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>10,52%</t>
+          <t>10,77%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>15,87%</t>
+          <t>16,02%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -7410,12 +7410,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>99213</t>
+          <t>101037</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>142522</t>
+          <t>142674</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -7425,12 +7425,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>13,44%</t>
+          <t>13,69%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>19,31%</t>
+          <t>19,33%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -7445,12 +7445,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>177562</t>
+          <t>178195</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>229512</t>
+          <t>231690</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -7460,12 +7460,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>13,07%</t>
+          <t>13,11%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>16,89%</t>
+          <t>17,05%</t>
         </is>
       </c>
     </row>
@@ -7488,12 +7488,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>522194</t>
+          <t>521283</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>555424</t>
+          <t>553845</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -7503,12 +7503,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>84,13%</t>
+          <t>83,98%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>89,48%</t>
+          <t>89,23%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -7523,12 +7523,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>595722</t>
+          <t>595570</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>639031</t>
+          <t>637207</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -7538,12 +7538,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>80,69%</t>
+          <t>80,67%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>86,56%</t>
+          <t>86,31%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -7558,12 +7558,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1129438</t>
+          <t>1127260</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1181388</t>
+          <t>1180755</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -7573,12 +7573,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>83,11%</t>
+          <t>82,95%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>86,93%</t>
+          <t>86,89%</t>
         </is>
       </c>
     </row>
@@ -7718,12 +7718,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>1086</t>
+          <t>1091</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>10591</t>
+          <t>10891</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -7738,7 +7738,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>3,69%</t>
+          <t>3,79%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -7753,12 +7753,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>159575</t>
+          <t>159400</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>213094</t>
+          <t>213871</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -7768,12 +7768,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>14,75%</t>
+          <t>14,73%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>19,69%</t>
+          <t>19,77%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -7788,12 +7788,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>164623</t>
+          <t>163838</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>217986</t>
+          <t>218375</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -7803,12 +7803,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>12,02%</t>
+          <t>11,97%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>15,92%</t>
+          <t>15,95%</t>
         </is>
       </c>
     </row>
@@ -7831,12 +7831,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>276554</t>
+          <t>276254</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>286059</t>
+          <t>286054</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -7846,7 +7846,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>96,31%</t>
+          <t>96,21%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -7866,12 +7866,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>868931</t>
+          <t>868154</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>922450</t>
+          <t>922625</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -7881,12 +7881,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>80,31%</t>
+          <t>80,23%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>85,25%</t>
+          <t>85,27%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -7901,12 +7901,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>1151184</t>
+          <t>1150795</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>1204547</t>
+          <t>1205332</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -7916,12 +7916,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>84,08%</t>
+          <t>84,05%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>87,98%</t>
+          <t>88,03%</t>
         </is>
       </c>
     </row>
@@ -8061,12 +8061,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>355639</t>
+          <t>353144</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>426848</t>
+          <t>425946</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -8076,12 +8076,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>10,5%</t>
+          <t>10,43%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>12,61%</t>
+          <t>12,58%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -8096,12 +8096,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>425744</t>
+          <t>425322</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>508197</t>
+          <t>509793</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -8111,12 +8111,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>12,06%</t>
+          <t>12,04%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>14,39%</t>
+          <t>14,44%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -8131,12 +8131,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>797339</t>
+          <t>799535</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>914295</t>
+          <t>913353</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -8146,12 +8146,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>11,53%</t>
+          <t>11,56%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>13,22%</t>
+          <t>13,2%</t>
         </is>
       </c>
     </row>
@@ -8174,12 +8174,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>2958874</t>
+          <t>2959776</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>3030083</t>
+          <t>3032578</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -8189,12 +8189,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>87,39%</t>
+          <t>87,42%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>89,5%</t>
+          <t>89,57%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -8209,12 +8209,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>3023399</t>
+          <t>3021803</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>3105852</t>
+          <t>3106274</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -8224,12 +8224,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>85,61%</t>
+          <t>85,56%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>87,94%</t>
+          <t>87,96%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -8244,12 +8244,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>6003023</t>
+          <t>6003965</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>6119979</t>
+          <t>6117783</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -8259,12 +8259,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>86,78%</t>
+          <t>86,8%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>88,47%</t>
+          <t>88,44%</t>
         </is>
       </c>
     </row>
@@ -8443,7 +8443,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con diagnóstico de colesterol alto en 2023</t>
+          <t>Población con diagnóstico de colesterol alto en 2023 (tasa de respuesta: 99,76%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -8638,12 +8638,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>54721</t>
+          <t>53779</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>83475</t>
+          <t>82603</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -8653,12 +8653,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>10,83%</t>
+          <t>10,64%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>16,52%</t>
+          <t>16,35%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -8673,12 +8673,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>50770</t>
+          <t>50050</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>73618</t>
+          <t>72456</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -8688,12 +8688,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>11,35%</t>
+          <t>11,19%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>16,45%</t>
+          <t>16,19%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -8708,12 +8708,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>111667</t>
+          <t>109652</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>147469</t>
+          <t>147639</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -8723,12 +8723,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>11,72%</t>
+          <t>11,51%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>15,48%</t>
+          <t>15,5%</t>
         </is>
       </c>
     </row>
@@ -8751,12 +8751,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>421737</t>
+          <t>422609</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>450491</t>
+          <t>451433</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -8766,12 +8766,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>83,48%</t>
+          <t>83,65%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>89,17%</t>
+          <t>89,36%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -8786,12 +8786,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>373849</t>
+          <t>375011</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>396697</t>
+          <t>397417</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -8801,12 +8801,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>83,55%</t>
+          <t>83,81%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>88,65%</t>
+          <t>88,81%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -8821,12 +8821,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>805210</t>
+          <t>805040</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>841012</t>
+          <t>843027</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -8836,12 +8836,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>84,52%</t>
+          <t>84,5%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>88,28%</t>
+          <t>88,49%</t>
         </is>
       </c>
     </row>
@@ -8981,12 +8981,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>59059</t>
+          <t>59782</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>87164</t>
+          <t>88038</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -8996,12 +8996,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>13,09%</t>
+          <t>13,25%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>19,32%</t>
+          <t>19,52%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -9016,12 +9016,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>33447</t>
+          <t>33902</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>52288</t>
+          <t>52234</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -9031,12 +9031,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>8,77%</t>
+          <t>8,89%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>13,71%</t>
+          <t>13,7%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -9051,12 +9051,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>96975</t>
+          <t>97280</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>132053</t>
+          <t>132104</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -9066,12 +9066,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>11,65%</t>
+          <t>11,69%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>15,86%</t>
+          <t>15,87%</t>
         </is>
       </c>
     </row>
@@ -9094,12 +9094,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>363963</t>
+          <t>363089</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>392068</t>
+          <t>391345</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -9109,12 +9109,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>80,68%</t>
+          <t>80,48%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>86,91%</t>
+          <t>86,75%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -9129,12 +9129,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>329029</t>
+          <t>329083</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>347870</t>
+          <t>347415</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -9144,12 +9144,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>86,29%</t>
+          <t>86,3%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>91,23%</t>
+          <t>91,11%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -9164,12 +9164,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>700392</t>
+          <t>700341</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>735470</t>
+          <t>735165</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -9179,12 +9179,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>84,14%</t>
+          <t>84,13%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>88,35%</t>
+          <t>88,31%</t>
         </is>
       </c>
     </row>
@@ -9324,12 +9324,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>29443</t>
+          <t>30010</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>125368</t>
+          <t>126384</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -9339,12 +9339,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>4,41%</t>
+          <t>4,5%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>18,78%</t>
+          <t>18,93%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -9359,12 +9359,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>26206</t>
+          <t>26210</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>41933</t>
+          <t>41087</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -9379,7 +9379,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>25,22%</t>
+          <t>24,71%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -9394,12 +9394,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>45687</t>
+          <t>39912</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>161768</t>
+          <t>158812</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -9409,12 +9409,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>5,48%</t>
+          <t>4,79%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>19,4%</t>
+          <t>19,05%</t>
         </is>
       </c>
     </row>
@@ -9437,12 +9437,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>542177</t>
+          <t>541161</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>638102</t>
+          <t>637535</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -9452,12 +9452,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>81,22%</t>
+          <t>81,07%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>95,59%</t>
+          <t>95,5%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -9472,12 +9472,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>124359</t>
+          <t>125205</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>140086</t>
+          <t>140082</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -9487,7 +9487,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>74,78%</t>
+          <t>75,29%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -9507,12 +9507,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>672069</t>
+          <t>675025</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>788150</t>
+          <t>793925</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -9522,12 +9522,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>80,6%</t>
+          <t>80,95%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>94,52%</t>
+          <t>95,21%</t>
         </is>
       </c>
     </row>
@@ -9667,12 +9667,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>140877</t>
+          <t>138420</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>181746</t>
+          <t>181935</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -9682,12 +9682,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>13,67%</t>
+          <t>13,43%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>17,63%</t>
+          <t>17,65%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -9702,12 +9702,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>118251</t>
+          <t>119805</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>628836</t>
+          <t>628302</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -9717,12 +9717,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>12,1%</t>
+          <t>12,26%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>64,33%</t>
+          <t>64,27%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -9737,12 +9737,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>279792</t>
+          <t>279901</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>912637</t>
+          <t>906774</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -9752,12 +9752,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>13,93%</t>
+          <t>13,94%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>45,44%</t>
+          <t>45,15%</t>
         </is>
       </c>
     </row>
@@ -9780,12 +9780,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>849158</t>
+          <t>848969</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>890027</t>
+          <t>892484</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -9795,12 +9795,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>82,37%</t>
+          <t>82,35%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>86,33%</t>
+          <t>86,57%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -9815,12 +9815,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>348724</t>
+          <t>349258</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>859309</t>
+          <t>857755</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -9830,12 +9830,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>35,67%</t>
+          <t>35,73%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>87,9%</t>
+          <t>87,74%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -9850,12 +9850,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1095827</t>
+          <t>1101690</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1728672</t>
+          <t>1728563</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -9865,12 +9865,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>54,56%</t>
+          <t>54,85%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>86,07%</t>
+          <t>86,06%</t>
         </is>
       </c>
     </row>
@@ -10010,12 +10010,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>62951</t>
+          <t>63948</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>92037</t>
+          <t>93520</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -10025,12 +10025,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>13,32%</t>
+          <t>13,53%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>19,47%</t>
+          <t>19,78%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -10045,12 +10045,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>124352</t>
+          <t>126286</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>198811</t>
+          <t>199600</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -10060,12 +10060,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>14,85%</t>
+          <t>15,08%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>23,74%</t>
+          <t>23,84%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -10080,12 +10080,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>209563</t>
+          <t>205010</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>284345</t>
+          <t>280976</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -10095,12 +10095,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>16,0%</t>
+          <t>15,65%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>21,7%</t>
+          <t>21,45%</t>
         </is>
       </c>
     </row>
@@ -10123,12 +10123,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>380690</t>
+          <t>379207</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>409776</t>
+          <t>408779</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -10138,12 +10138,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>80,53%</t>
+          <t>80,22%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>86,68%</t>
+          <t>86,47%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -10158,12 +10158,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>638514</t>
+          <t>637725</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>712973</t>
+          <t>711039</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -10173,12 +10173,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>76,26%</t>
+          <t>76,16%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>85,15%</t>
+          <t>84,92%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -10193,12 +10193,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1025707</t>
+          <t>1029076</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1100489</t>
+          <t>1105042</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -10208,12 +10208,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>78,3%</t>
+          <t>78,55%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>84,0%</t>
+          <t>84,35%</t>
         </is>
       </c>
     </row>
@@ -10353,12 +10353,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>2076</t>
+          <t>2051</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>11175</t>
+          <t>11727</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -10368,12 +10368,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>0,86%</t>
+          <t>0,85%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>4,65%</t>
+          <t>4,88%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -10388,12 +10388,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>122054</t>
+          <t>122213</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>154982</t>
+          <t>154310</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -10403,12 +10403,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>16,05%</t>
+          <t>16,07%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>20,38%</t>
+          <t>20,3%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -10423,12 +10423,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>123812</t>
+          <t>126122</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>158597</t>
+          <t>162299</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -10438,12 +10438,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>12,37%</t>
+          <t>12,6%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>15,85%</t>
+          <t>16,22%</t>
         </is>
       </c>
     </row>
@@ -10466,12 +10466,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>229332</t>
+          <t>228780</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>238431</t>
+          <t>238456</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -10481,12 +10481,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>95,35%</t>
+          <t>95,12%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>99,14%</t>
+          <t>99,15%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -10501,12 +10501,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>605312</t>
+          <t>605984</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>638240</t>
+          <t>638081</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -10516,12 +10516,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>79,62%</t>
+          <t>79,7%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>83,95%</t>
+          <t>83,93%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -10536,12 +10536,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>842204</t>
+          <t>838502</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>876989</t>
+          <t>874679</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -10551,12 +10551,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>84,15%</t>
+          <t>83,78%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>87,63%</t>
+          <t>87,4%</t>
         </is>
       </c>
     </row>
@@ -10696,12 +10696,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>351284</t>
+          <t>347790</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>507275</t>
+          <t>507987</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -10711,12 +10711,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>10,43%</t>
+          <t>10,33%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>15,06%</t>
+          <t>15,08%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -10731,12 +10731,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>560378</t>
+          <t>561405</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>1211963</t>
+          <t>1325870</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -10746,12 +10746,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>15,7%</t>
+          <t>15,72%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>33,95%</t>
+          <t>37,14%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -10766,12 +10766,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>1000992</t>
+          <t>1010014</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>1982546</t>
+          <t>1880507</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -10781,12 +10781,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>14,43%</t>
+          <t>14,56%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>28,57%</t>
+          <t>27,1%</t>
         </is>
       </c>
     </row>
@@ -10809,12 +10809,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>2860748</t>
+          <t>2860036</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>3016739</t>
+          <t>3020233</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -10824,12 +10824,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>84,94%</t>
+          <t>84,92%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>89,57%</t>
+          <t>89,67%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -10844,12 +10844,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>2358292</t>
+          <t>2244385</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>3009877</t>
+          <t>3008850</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -10859,12 +10859,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>66,05%</t>
+          <t>62,86%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>84,3%</t>
+          <t>84,28%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -10879,12 +10879,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>4955732</t>
+          <t>5057771</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>5937286</t>
+          <t>5928264</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -10894,12 +10894,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>71,43%</t>
+          <t>72,9%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>85,57%</t>
+          <t>85,44%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P1404-Clase-trans_orig.xlsx
+++ b/data/trans_orig/P1404-Clase-trans_orig.xlsx
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>21519</t>
+          <t>20723</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>43171</t>
+          <t>43963</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>4,54%</t>
+          <t>4,37%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>9,11%</t>
+          <t>9,28%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>14498</t>
+          <t>13038</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>31931</t>
+          <t>31720</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>4,73%</t>
+          <t>4,25%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>10,41%</t>
+          <t>10,34%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>38887</t>
+          <t>38893</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>68372</t>
+          <t>65780</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -823,7 +823,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>8,76%</t>
+          <t>8,43%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>430605</t>
+          <t>429813</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>452257</t>
+          <t>453053</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>90,89%</t>
+          <t>90,72%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>95,46%</t>
+          <t>95,63%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>274749</t>
+          <t>274960</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>292182</t>
+          <t>293642</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>89,59%</t>
+          <t>89,66%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>95,27%</t>
+          <t>95,75%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>712085</t>
+          <t>714677</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>741570</t>
+          <t>741564</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,7 +931,7 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>91,24%</t>
+          <t>91,57%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>20331</t>
+          <t>20701</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>41354</t>
+          <t>41806</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>5,54%</t>
+          <t>5,64%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>11,27%</t>
+          <t>11,39%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1116,7 +1116,7 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>34004</t>
+          <t>34463</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1131,7 +1131,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>9,14%</t>
+          <t>9,27%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>40091</t>
+          <t>39997</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>68264</t>
+          <t>68807</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>5,43%</t>
+          <t>5,41%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>9,24%</t>
+          <t>9,31%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>325580</t>
+          <t>325128</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>346603</t>
+          <t>346233</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>88,73%</t>
+          <t>88,61%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>94,46%</t>
+          <t>94,36%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,7 +1224,7 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>337861</t>
+          <t>337402</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
@@ -1239,7 +1239,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>90,86%</t>
+          <t>90,73%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>670535</t>
+          <t>669992</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>698708</t>
+          <t>698802</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>90,76%</t>
+          <t>90,69%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>94,57%</t>
+          <t>94,59%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>43571</t>
+          <t>43516</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>71389</t>
+          <t>73364</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>8,03%</t>
+          <t>8,02%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>13,16%</t>
+          <t>13,53%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>9333</t>
+          <t>9893</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>24408</t>
+          <t>25517</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>5,56%</t>
+          <t>5,9%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>14,55%</t>
+          <t>15,21%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>56606</t>
+          <t>58823</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>87630</t>
+          <t>91566</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>7,97%</t>
+          <t>8,28%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>12,34%</t>
+          <t>12,89%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>471000</t>
+          <t>469025</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>498818</t>
+          <t>498873</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>86,84%</t>
+          <t>86,47%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>91,97%</t>
+          <t>91,98%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>143374</t>
+          <t>142265</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>158449</t>
+          <t>157889</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>85,45%</t>
+          <t>84,79%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>94,44%</t>
+          <t>94,1%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>622541</t>
+          <t>618605</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>653565</t>
+          <t>651348</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>87,66%</t>
+          <t>87,11%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>92,03%</t>
+          <t>91,72%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>93535</t>
+          <t>93500</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>133668</t>
+          <t>132215</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1782,7 +1782,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>10,79%</t>
+          <t>10,68%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>42528</t>
+          <t>40560</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>69682</t>
+          <t>67806</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>5,95%</t>
+          <t>5,68%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>9,76%</t>
+          <t>9,49%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>145430</t>
+          <t>142446</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>192362</t>
+          <t>192118</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>7,45%</t>
+          <t>7,3%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>9,85%</t>
+          <t>9,84%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>1104666</t>
+          <t>1106119</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>1144799</t>
+          <t>1144834</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,7 +1890,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>89,21%</t>
+          <t>89,32%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>644603</t>
+          <t>646479</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>671757</t>
+          <t>673725</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>90,24%</t>
+          <t>90,51%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>94,05%</t>
+          <t>94,32%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1760258</t>
+          <t>1760502</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1807190</t>
+          <t>1810174</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>90,15%</t>
+          <t>90,16%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>92,55%</t>
+          <t>92,7%</t>
         </is>
       </c>
     </row>
@@ -2105,12 +2105,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>18570</t>
+          <t>18703</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>37350</t>
+          <t>36883</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2120,12 +2120,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>5,3%</t>
+          <t>5,34%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>10,65%</t>
+          <t>10,52%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>47077</t>
+          <t>48441</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>79137</t>
+          <t>78117</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2155,12 +2155,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>8,28%</t>
+          <t>8,52%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>13,91%</t>
+          <t>13,73%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>68856</t>
+          <t>70532</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>105859</t>
+          <t>107268</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>7,49%</t>
+          <t>7,67%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>11,52%</t>
+          <t>11,67%</t>
         </is>
       </c>
     </row>
@@ -2218,12 +2218,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>313205</t>
+          <t>313672</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>331985</t>
+          <t>331852</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>89,35%</t>
+          <t>89,48%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>94,7%</t>
+          <t>94,66%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2253,12 +2253,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>489615</t>
+          <t>490635</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>521675</t>
+          <t>520311</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2268,12 +2268,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>86,09%</t>
+          <t>86,27%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>91,72%</t>
+          <t>91,48%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>813448</t>
+          <t>812039</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>850451</t>
+          <t>848775</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>88,48%</t>
+          <t>88,33%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>92,51%</t>
+          <t>92,33%</t>
         </is>
       </c>
     </row>
@@ -2428,7 +2428,7 @@
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -2448,12 +2448,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>909</t>
+          <t>895</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>8109</t>
+          <t>7810</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2468,7 +2468,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>2,72%</t>
+          <t>2,62%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2483,12 +2483,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>146871</t>
+          <t>149793</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>196715</t>
+          <t>198993</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2498,12 +2498,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>11,76%</t>
+          <t>12,0%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>15,75%</t>
+          <t>15,94%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2518,12 +2518,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>150861</t>
+          <t>150356</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>201932</t>
+          <t>200568</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2533,12 +2533,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>9,75%</t>
+          <t>9,72%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>13,05%</t>
+          <t>12,97%</t>
         </is>
       </c>
     </row>
@@ -2561,12 +2561,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>290092</t>
+          <t>290391</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>297292</t>
+          <t>297306</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2576,7 +2576,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>97,28%</t>
+          <t>97,38%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -2596,12 +2596,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>1052045</t>
+          <t>1049767</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>1101889</t>
+          <t>1098967</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2611,12 +2611,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>84,25%</t>
+          <t>84,06%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>88,24%</t>
+          <t>88,0%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2631,12 +2631,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>1345028</t>
+          <t>1346392</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>1396099</t>
+          <t>1396604</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2646,12 +2646,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>86,95%</t>
+          <t>87,03%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>90,25%</t>
+          <t>90,28%</t>
         </is>
       </c>
     </row>
@@ -2791,12 +2791,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>229426</t>
+          <t>229992</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>290099</t>
+          <t>291815</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2806,12 +2806,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>7,02%</t>
+          <t>7,03%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>8,87%</t>
+          <t>8,92%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2826,12 +2826,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>313868</t>
+          <t>314819</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>386536</t>
+          <t>385313</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2841,12 +2841,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>9,29%</t>
+          <t>9,32%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>11,44%</t>
+          <t>11,41%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>559925</t>
+          <t>563996</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>659148</t>
+          <t>658371</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2876,12 +2876,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>8,42%</t>
+          <t>8,48%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>9,91%</t>
+          <t>9,9%</t>
         </is>
       </c>
     </row>
@@ -2904,12 +2904,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>2980091</t>
+          <t>2978375</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>3040764</t>
+          <t>3040198</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>91,13%</t>
+          <t>91,08%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>92,98%</t>
+          <t>92,97%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2939,12 +2939,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>2991588</t>
+          <t>2992811</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>3064256</t>
+          <t>3063305</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2954,12 +2954,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>88,56%</t>
+          <t>88,59%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>90,71%</t>
+          <t>90,68%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2974,12 +2974,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>5989166</t>
+          <t>5989943</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>6088389</t>
+          <t>6084318</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2989,12 +2989,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>90,09%</t>
+          <t>90,1%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>91,58%</t>
+          <t>91,52%</t>
         </is>
       </c>
     </row>
@@ -3368,12 +3368,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>28945</t>
+          <t>30237</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>55838</t>
+          <t>57678</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3383,12 +3383,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>6,62%</t>
+          <t>6,92%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>12,77%</t>
+          <t>13,19%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3403,12 +3403,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>12221</t>
+          <t>11538</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>30914</t>
+          <t>29603</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3418,12 +3418,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>3,89%</t>
+          <t>3,67%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>9,83%</t>
+          <t>9,41%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3438,12 +3438,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>46315</t>
+          <t>46731</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>78769</t>
+          <t>78161</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3453,12 +3453,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>6,16%</t>
+          <t>6,22%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>10,48%</t>
+          <t>10,4%</t>
         </is>
       </c>
     </row>
@@ -3481,12 +3481,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>381373</t>
+          <t>379533</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>408266</t>
+          <t>406974</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -3496,12 +3496,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>87,23%</t>
+          <t>86,81%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>93,38%</t>
+          <t>93,08%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -3516,12 +3516,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>283540</t>
+          <t>284851</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>302233</t>
+          <t>302916</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -3531,12 +3531,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>90,17%</t>
+          <t>90,59%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>96,11%</t>
+          <t>96,33%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -3551,12 +3551,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>672896</t>
+          <t>673504</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>705350</t>
+          <t>704934</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3566,12 +3566,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>89,52%</t>
+          <t>89,6%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>93,84%</t>
+          <t>93,78%</t>
         </is>
       </c>
     </row>
@@ -3711,12 +3711,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>26542</t>
+          <t>25928</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>51735</t>
+          <t>50187</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -3726,12 +3726,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>6,34%</t>
+          <t>6,19%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>12,35%</t>
+          <t>11,98%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -3746,12 +3746,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>16082</t>
+          <t>15819</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>35630</t>
+          <t>36450</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -3761,12 +3761,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>4,76%</t>
+          <t>4,68%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>10,54%</t>
+          <t>10,78%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3781,12 +3781,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>47920</t>
+          <t>48793</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>78997</t>
+          <t>81606</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3796,12 +3796,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>6,33%</t>
+          <t>6,45%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>10,44%</t>
+          <t>10,78%</t>
         </is>
       </c>
     </row>
@@ -3824,12 +3824,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>367062</t>
+          <t>368610</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>392255</t>
+          <t>392869</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -3839,12 +3839,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>87,65%</t>
+          <t>88,02%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>93,66%</t>
+          <t>93,81%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -3859,12 +3859,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>302381</t>
+          <t>301561</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>321929</t>
+          <t>322192</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -3874,12 +3874,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>89,46%</t>
+          <t>89,22%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>95,24%</t>
+          <t>95,32%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3894,12 +3894,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>677811</t>
+          <t>675202</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>708888</t>
+          <t>708015</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3909,12 +3909,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>89,56%</t>
+          <t>89,22%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>93,67%</t>
+          <t>93,55%</t>
         </is>
       </c>
     </row>
@@ -4054,12 +4054,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>69599</t>
+          <t>68737</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>105815</t>
+          <t>105145</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4069,12 +4069,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>11,08%</t>
+          <t>10,95%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>16,85%</t>
+          <t>16,74%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4089,12 +4089,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>14856</t>
+          <t>14499</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>33834</t>
+          <t>34152</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4104,12 +4104,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>5,71%</t>
+          <t>5,57%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>13,01%</t>
+          <t>13,13%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4124,12 +4124,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>89903</t>
+          <t>90022</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>130162</t>
+          <t>133115</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4139,12 +4139,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>10,12%</t>
+          <t>10,14%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>14,66%</t>
+          <t>14,99%</t>
         </is>
       </c>
     </row>
@@ -4167,12 +4167,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>522191</t>
+          <t>522861</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>558407</t>
+          <t>559269</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4182,12 +4182,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>83,15%</t>
+          <t>83,26%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>88,92%</t>
+          <t>89,05%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4202,12 +4202,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>226295</t>
+          <t>225977</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>245273</t>
+          <t>245630</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4217,12 +4217,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>86,99%</t>
+          <t>86,87%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>94,29%</t>
+          <t>94,43%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4237,12 +4237,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>757974</t>
+          <t>755021</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>798233</t>
+          <t>798114</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4252,12 +4252,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>85,34%</t>
+          <t>85,01%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>89,88%</t>
+          <t>89,86%</t>
         </is>
       </c>
     </row>
@@ -4397,12 +4397,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>131885</t>
+          <t>132878</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>178574</t>
+          <t>183590</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4412,12 +4412,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>11,38%</t>
+          <t>11,46%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>15,41%</t>
+          <t>15,84%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -4432,12 +4432,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>54725</t>
+          <t>56781</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>88817</t>
+          <t>90554</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -4447,12 +4447,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>7,16%</t>
+          <t>7,42%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>11,61%</t>
+          <t>11,84%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -4467,12 +4467,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>199080</t>
+          <t>198375</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>255995</t>
+          <t>257040</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4482,12 +4482,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>10,35%</t>
+          <t>10,31%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>13,31%</t>
+          <t>13,36%</t>
         </is>
       </c>
     </row>
@@ -4510,12 +4510,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>980435</t>
+          <t>975419</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>1027124</t>
+          <t>1026131</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4525,12 +4525,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>84,59%</t>
+          <t>84,16%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>88,62%</t>
+          <t>88,54%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -4545,12 +4545,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>675905</t>
+          <t>674168</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>709997</t>
+          <t>707941</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -4560,12 +4560,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>88,39%</t>
+          <t>88,16%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>92,84%</t>
+          <t>92,58%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -4580,12 +4580,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1667736</t>
+          <t>1666691</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1724651</t>
+          <t>1725356</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4595,12 +4595,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>86,69%</t>
+          <t>86,64%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>89,65%</t>
+          <t>89,69%</t>
         </is>
       </c>
     </row>
@@ -4740,12 +4740,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>51101</t>
+          <t>50798</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>81359</t>
+          <t>82300</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4755,12 +4755,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>10,01%</t>
+          <t>9,95%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>15,93%</t>
+          <t>16,12%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4775,12 +4775,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>114775</t>
+          <t>113534</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>155658</t>
+          <t>156339</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4790,12 +4790,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>15,1%</t>
+          <t>14,93%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>20,47%</t>
+          <t>20,56%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4810,12 +4810,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>170093</t>
+          <t>168852</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>224285</t>
+          <t>225032</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4825,12 +4825,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>13,38%</t>
+          <t>13,29%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>17,65%</t>
+          <t>17,71%</t>
         </is>
       </c>
     </row>
@@ -4853,12 +4853,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>429237</t>
+          <t>428296</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>459495</t>
+          <t>459798</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4868,12 +4868,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>84,07%</t>
+          <t>83,88%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>89,99%</t>
+          <t>90,05%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4888,12 +4888,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>604588</t>
+          <t>603907</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>645471</t>
+          <t>646712</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4903,12 +4903,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>79,53%</t>
+          <t>79,44%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>84,9%</t>
+          <t>85,07%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4923,12 +4923,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1046558</t>
+          <t>1045811</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1100750</t>
+          <t>1101991</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4938,12 +4938,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>82,35%</t>
+          <t>82,29%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>86,62%</t>
+          <t>86,71%</t>
         </is>
       </c>
     </row>
@@ -5063,7 +5063,7 @@
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -5083,12 +5083,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>935</t>
+          <t>932</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>11544</t>
+          <t>10549</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5103,7 +5103,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>4,33%</t>
+          <t>3,95%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5118,12 +5118,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>191314</t>
+          <t>188399</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>246106</t>
+          <t>244916</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5133,12 +5133,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>17,25%</t>
+          <t>16,98%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>22,18%</t>
+          <t>22,08%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5153,12 +5153,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>192296</t>
+          <t>194576</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>249468</t>
+          <t>248831</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5168,12 +5168,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>13,97%</t>
+          <t>14,14%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>18,13%</t>
+          <t>18,08%</t>
         </is>
       </c>
     </row>
@@ -5196,12 +5196,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>255338</t>
+          <t>256333</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>265947</t>
+          <t>265950</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5211,7 +5211,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>95,67%</t>
+          <t>96,05%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -5231,12 +5231,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>863245</t>
+          <t>864435</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>918037</t>
+          <t>920952</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5246,12 +5246,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>77,82%</t>
+          <t>77,92%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>82,75%</t>
+          <t>83,02%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5266,12 +5266,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>1126765</t>
+          <t>1127402</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>1183937</t>
+          <t>1181657</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5281,12 +5281,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>81,87%</t>
+          <t>81,92%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>86,03%</t>
+          <t>85,86%</t>
         </is>
       </c>
     </row>
@@ -5426,12 +5426,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>351597</t>
+          <t>352485</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>424285</t>
+          <t>429809</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5441,12 +5441,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>10,28%</t>
+          <t>10,31%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>12,4%</t>
+          <t>12,57%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5461,12 +5461,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>446738</t>
+          <t>446326</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>534749</t>
+          <t>535401</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5476,12 +5476,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>12,6%</t>
+          <t>12,58%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>15,08%</t>
+          <t>15,09%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5496,12 +5496,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>817685</t>
+          <t>825488</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>936645</t>
+          <t>939490</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5511,12 +5511,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>11,74%</t>
+          <t>11,85%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>13,44%</t>
+          <t>13,48%</t>
         </is>
       </c>
     </row>
@@ -5539,12 +5539,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>2996216</t>
+          <t>2990692</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>3068904</t>
+          <t>3068016</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -5554,12 +5554,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>87,6%</t>
+          <t>87,43%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>89,72%</t>
+          <t>89,69%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -5574,12 +5574,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>3012166</t>
+          <t>3011514</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>3100177</t>
+          <t>3100589</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -5589,12 +5589,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>84,92%</t>
+          <t>84,91%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>87,4%</t>
+          <t>87,42%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -5609,12 +5609,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>6030771</t>
+          <t>6027926</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>6149731</t>
+          <t>6141928</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -5624,12 +5624,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>86,56%</t>
+          <t>86,52%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>88,26%</t>
+          <t>88,15%</t>
         </is>
       </c>
     </row>
@@ -6003,12 +6003,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>33046</t>
+          <t>33247</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>58968</t>
+          <t>59547</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -6018,12 +6018,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>7,7%</t>
+          <t>7,75%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>13,74%</t>
+          <t>13,88%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6038,12 +6038,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>17946</t>
+          <t>18370</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>41615</t>
+          <t>41532</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -6053,12 +6053,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>5,17%</t>
+          <t>5,29%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>11,99%</t>
+          <t>11,97%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6073,12 +6073,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>56210</t>
+          <t>56005</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>91520</t>
+          <t>90659</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6088,12 +6088,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>7,24%</t>
+          <t>7,22%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>11,79%</t>
+          <t>11,68%</t>
         </is>
       </c>
     </row>
@@ -6116,12 +6116,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>370124</t>
+          <t>369545</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>396046</t>
+          <t>395845</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -6131,12 +6131,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>86,26%</t>
+          <t>86,12%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>92,3%</t>
+          <t>92,25%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -6151,12 +6151,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>305440</t>
+          <t>305523</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>329109</t>
+          <t>328685</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -6166,12 +6166,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>88,01%</t>
+          <t>88,03%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>94,83%</t>
+          <t>94,71%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6186,12 +6186,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>684627</t>
+          <t>685488</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>719937</t>
+          <t>720142</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -6201,12 +6201,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>88,21%</t>
+          <t>88,32%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>92,76%</t>
+          <t>92,78%</t>
         </is>
       </c>
     </row>
@@ -6346,12 +6346,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>28790</t>
+          <t>28813</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>53118</t>
+          <t>54603</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -6361,12 +6361,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>7,63%</t>
+          <t>7,64%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>14,08%</t>
+          <t>14,47%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -6381,12 +6381,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>22367</t>
+          <t>21424</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>44839</t>
+          <t>44988</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -6396,12 +6396,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>6,01%</t>
+          <t>5,75%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>12,04%</t>
+          <t>12,08%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -6416,12 +6416,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>56666</t>
+          <t>56165</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>90991</t>
+          <t>89832</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -6431,12 +6431,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>7,56%</t>
+          <t>7,49%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>12,14%</t>
+          <t>11,99%</t>
         </is>
       </c>
     </row>
@@ -6459,12 +6459,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>324109</t>
+          <t>322624</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>348437</t>
+          <t>348414</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -6474,12 +6474,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>85,92%</t>
+          <t>85,53%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>92,37%</t>
+          <t>92,36%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -6494,12 +6494,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>327434</t>
+          <t>327285</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>349906</t>
+          <t>350849</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -6509,12 +6509,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>87,96%</t>
+          <t>87,92%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>93,99%</t>
+          <t>94,25%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -6529,12 +6529,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>658509</t>
+          <t>659668</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>692834</t>
+          <t>693335</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -6544,12 +6544,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>87,86%</t>
+          <t>88,01%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>92,44%</t>
+          <t>92,51%</t>
         </is>
       </c>
     </row>
@@ -6689,12 +6689,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>58500</t>
+          <t>58385</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>89545</t>
+          <t>89772</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -6704,12 +6704,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>11,21%</t>
+          <t>11,19%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>17,16%</t>
+          <t>17,2%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -6724,12 +6724,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>14545</t>
+          <t>13929</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>33027</t>
+          <t>35615</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -6739,12 +6739,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>8,76%</t>
+          <t>8,38%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>19,88%</t>
+          <t>21,44%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6759,12 +6759,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>76877</t>
+          <t>76982</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>115129</t>
+          <t>114370</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -6774,12 +6774,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>11,17%</t>
+          <t>11,19%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>16,73%</t>
+          <t>16,62%</t>
         </is>
       </c>
     </row>
@@ -6802,12 +6802,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>432369</t>
+          <t>432142</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>463414</t>
+          <t>463529</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -6817,12 +6817,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>82,84%</t>
+          <t>82,8%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>88,79%</t>
+          <t>88,81%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -6837,12 +6837,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>133096</t>
+          <t>130508</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>151578</t>
+          <t>152194</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -6852,12 +6852,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>80,12%</t>
+          <t>78,56%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>91,24%</t>
+          <t>91,62%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -6872,12 +6872,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>572907</t>
+          <t>573666</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>611159</t>
+          <t>611054</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -6887,12 +6887,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>83,27%</t>
+          <t>83,38%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>88,83%</t>
+          <t>88,81%</t>
         </is>
       </c>
     </row>
@@ -7032,12 +7032,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>124573</t>
+          <t>126265</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>168528</t>
+          <t>169126</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -7047,12 +7047,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>10,84%</t>
+          <t>10,98%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>14,66%</t>
+          <t>14,71%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7067,12 +7067,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>62047</t>
+          <t>62236</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>95201</t>
+          <t>96290</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -7082,12 +7082,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>7,51%</t>
+          <t>7,54%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>11,53%</t>
+          <t>11,66%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7102,12 +7102,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>194329</t>
+          <t>194489</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>251847</t>
+          <t>250525</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -7122,7 +7122,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>12,75%</t>
+          <t>12,68%</t>
         </is>
       </c>
     </row>
@@ -7145,12 +7145,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>981110</t>
+          <t>980512</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>1025065</t>
+          <t>1023373</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -7160,12 +7160,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>85,34%</t>
+          <t>85,29%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>89,16%</t>
+          <t>89,02%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7180,12 +7180,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>730675</t>
+          <t>729586</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>763829</t>
+          <t>763640</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -7195,12 +7195,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>88,47%</t>
+          <t>88,34%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>92,49%</t>
+          <t>92,46%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7215,12 +7215,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1723667</t>
+          <t>1724989</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1781185</t>
+          <t>1781025</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -7230,7 +7230,7 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>87,25%</t>
+          <t>87,32%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
@@ -7375,12 +7375,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>66861</t>
+          <t>67241</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>99423</t>
+          <t>99486</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -7390,12 +7390,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>10,77%</t>
+          <t>10,83%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>16,02%</t>
+          <t>16,03%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -7410,12 +7410,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>101037</t>
+          <t>101366</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>142674</t>
+          <t>142176</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -7425,12 +7425,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>13,69%</t>
+          <t>13,73%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>19,33%</t>
+          <t>19,26%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -7445,12 +7445,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>178195</t>
+          <t>175585</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>231690</t>
+          <t>228376</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -7460,12 +7460,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>13,11%</t>
+          <t>12,92%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>17,05%</t>
+          <t>16,81%</t>
         </is>
       </c>
     </row>
@@ -7488,12 +7488,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>521283</t>
+          <t>521220</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>553845</t>
+          <t>553465</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -7503,12 +7503,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>83,98%</t>
+          <t>83,97%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>89,23%</t>
+          <t>89,17%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -7523,12 +7523,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>595570</t>
+          <t>596068</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>637207</t>
+          <t>636878</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -7538,12 +7538,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>80,67%</t>
+          <t>80,74%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>86,31%</t>
+          <t>86,27%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -7558,12 +7558,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1127260</t>
+          <t>1130574</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1180755</t>
+          <t>1183365</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -7573,12 +7573,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>82,95%</t>
+          <t>83,19%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>86,89%</t>
+          <t>87,08%</t>
         </is>
       </c>
     </row>
@@ -7698,7 +7698,7 @@
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -7718,12 +7718,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>1091</t>
+          <t>1128</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>10891</t>
+          <t>11171</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -7733,12 +7733,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>0,38%</t>
+          <t>0,39%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>3,79%</t>
+          <t>3,89%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -7753,12 +7753,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>159400</t>
+          <t>160413</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>213871</t>
+          <t>212038</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -7768,12 +7768,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>14,73%</t>
+          <t>14,83%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>19,77%</t>
+          <t>19,6%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -7788,12 +7788,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>163838</t>
+          <t>163912</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>218375</t>
+          <t>217842</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -7808,7 +7808,7 @@
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>15,95%</t>
+          <t>15,91%</t>
         </is>
       </c>
     </row>
@@ -7831,12 +7831,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>276254</t>
+          <t>275974</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>286054</t>
+          <t>286017</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -7846,12 +7846,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>96,21%</t>
+          <t>96,11%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>99,62%</t>
+          <t>99,61%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -7866,12 +7866,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>868154</t>
+          <t>869987</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>922625</t>
+          <t>921612</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -7881,12 +7881,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>80,23%</t>
+          <t>80,4%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>85,27%</t>
+          <t>85,17%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -7901,12 +7901,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>1150795</t>
+          <t>1151328</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>1205332</t>
+          <t>1205258</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -7916,7 +7916,7 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>84,05%</t>
+          <t>84,09%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
@@ -8061,12 +8061,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>353144</t>
+          <t>355260</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>425946</t>
+          <t>427242</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -8076,12 +8076,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>10,43%</t>
+          <t>10,49%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>12,58%</t>
+          <t>12,62%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -8096,12 +8096,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>425322</t>
+          <t>426805</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>509793</t>
+          <t>510138</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -8111,7 +8111,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>12,04%</t>
+          <t>12,09%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -8131,12 +8131,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>799535</t>
+          <t>803014</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>913353</t>
+          <t>919145</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -8146,12 +8146,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>11,56%</t>
+          <t>11,61%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>13,2%</t>
+          <t>13,29%</t>
         </is>
       </c>
     </row>
@@ -8174,12 +8174,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>2959776</t>
+          <t>2958480</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>3032578</t>
+          <t>3030462</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -8189,12 +8189,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>87,42%</t>
+          <t>87,38%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>89,57%</t>
+          <t>89,51%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -8209,12 +8209,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>3021803</t>
+          <t>3021458</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>3106274</t>
+          <t>3104791</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -8229,7 +8229,7 @@
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>87,96%</t>
+          <t>87,91%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -8244,12 +8244,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>6003965</t>
+          <t>5998173</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>6117783</t>
+          <t>6114304</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -8259,12 +8259,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>86,8%</t>
+          <t>86,71%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>88,44%</t>
+          <t>88,39%</t>
         </is>
       </c>
     </row>
@@ -8633,32 +8633,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>67527</t>
+          <t>75808</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>53779</t>
+          <t>62425</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>82603</t>
+          <t>91819</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>13,37%</t>
+          <t>13,77%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>10,64%</t>
+          <t>11,34%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>16,35%</t>
+          <t>16,68%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -8668,32 +8668,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>60725</t>
+          <t>65830</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>50050</t>
+          <t>53863</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>72456</t>
+          <t>79250</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>13,57%</t>
+          <t>13,48%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>11,19%</t>
+          <t>11,03%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>16,19%</t>
+          <t>16,23%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -8703,32 +8703,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>128252</t>
+          <t>141639</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>109652</t>
+          <t>124519</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>147639</t>
+          <t>161944</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>13,46%</t>
+          <t>13,63%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>11,51%</t>
+          <t>11,98%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>15,5%</t>
+          <t>15,59%</t>
         </is>
       </c>
     </row>
@@ -8746,32 +8746,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>437685</t>
+          <t>474810</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>422609</t>
+          <t>458799</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>451433</t>
+          <t>488193</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>86,63%</t>
+          <t>86,23%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>83,65%</t>
+          <t>83,32%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>89,36%</t>
+          <t>88,66%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -8781,32 +8781,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>386742</t>
+          <t>422581</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>375011</t>
+          <t>409161</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>397417</t>
+          <t>434548</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>86,43%</t>
+          <t>86,52%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>83,81%</t>
+          <t>83,77%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>88,81%</t>
+          <t>88,97%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -8816,32 +8816,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>824427</t>
+          <t>897390</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>805040</t>
+          <t>877085</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>843027</t>
+          <t>914510</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>86,54%</t>
+          <t>86,37%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>84,5%</t>
+          <t>84,41%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>88,49%</t>
+          <t>88,02%</t>
         </is>
       </c>
     </row>
@@ -8859,17 +8859,17 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>505212</t>
+          <t>550618</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>505212</t>
+          <t>550618</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>505212</t>
+          <t>550618</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -8894,17 +8894,17 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>447467</t>
+          <t>488411</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>447467</t>
+          <t>488411</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>447467</t>
+          <t>488411</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -8929,17 +8929,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>952679</t>
+          <t>1039029</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>952679</t>
+          <t>1039029</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>952679</t>
+          <t>1039029</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -8976,32 +8976,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>72110</t>
+          <t>78133</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>59782</t>
+          <t>63579</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>88038</t>
+          <t>94748</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>15,98%</t>
+          <t>16,21%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>13,25%</t>
+          <t>13,19%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>19,52%</t>
+          <t>19,65%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -9011,32 +9011,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>42301</t>
+          <t>46421</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>33902</t>
+          <t>37252</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>52234</t>
+          <t>56234</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>11,09%</t>
+          <t>11,0%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>8,89%</t>
+          <t>8,83%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>13,7%</t>
+          <t>13,33%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -9046,32 +9046,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>114412</t>
+          <t>124553</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>97280</t>
+          <t>107511</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>132104</t>
+          <t>143323</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>13,74%</t>
+          <t>13,78%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>11,69%</t>
+          <t>11,89%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>15,87%</t>
+          <t>15,85%</t>
         </is>
       </c>
     </row>
@@ -9089,32 +9089,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>379017</t>
+          <t>403943</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>363089</t>
+          <t>387328</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>391345</t>
+          <t>418497</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>84,02%</t>
+          <t>83,79%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>80,48%</t>
+          <t>80,35%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>86,75%</t>
+          <t>86,81%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -9124,32 +9124,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>339016</t>
+          <t>375465</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>329083</t>
+          <t>365652</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>347415</t>
+          <t>384634</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>88,91%</t>
+          <t>89,0%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>86,3%</t>
+          <t>86,67%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>91,11%</t>
+          <t>91,17%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -9159,32 +9159,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>718033</t>
+          <t>779408</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>700341</t>
+          <t>760638</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>735165</t>
+          <t>796450</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>86,26%</t>
+          <t>86,22%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>84,13%</t>
+          <t>84,15%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>88,31%</t>
+          <t>88,11%</t>
         </is>
       </c>
     </row>
@@ -9202,17 +9202,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>451127</t>
+          <t>482076</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>451127</t>
+          <t>482076</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>451127</t>
+          <t>482076</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -9237,17 +9237,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>381317</t>
+          <t>421886</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>381317</t>
+          <t>421886</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>381317</t>
+          <t>421886</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -9272,17 +9272,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>832445</t>
+          <t>903961</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>832445</t>
+          <t>903961</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>832445</t>
+          <t>903961</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -9319,32 +9319,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>74992</t>
+          <t>81085</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>30010</t>
+          <t>67133</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>126384</t>
+          <t>97005</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>11,23%</t>
+          <t>17,22%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>4,5%</t>
+          <t>14,26%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>18,93%</t>
+          <t>20,61%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -9354,32 +9354,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>33282</t>
+          <t>36338</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>26210</t>
+          <t>28711</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>41087</t>
+          <t>45582</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>20,01%</t>
+          <t>19,45%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>15,76%</t>
+          <t>15,37%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>24,71%</t>
+          <t>24,4%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -9389,32 +9389,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>108273</t>
+          <t>117423</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>39912</t>
+          <t>99801</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>158812</t>
+          <t>134011</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>12,98%</t>
+          <t>17,86%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>4,79%</t>
+          <t>15,18%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>19,05%</t>
+          <t>20,38%</t>
         </is>
       </c>
     </row>
@@ -9432,32 +9432,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>592553</t>
+          <t>389658</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>541161</t>
+          <t>373738</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>637535</t>
+          <t>403610</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>88,77%</t>
+          <t>82,78%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>81,07%</t>
+          <t>79,39%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>95,5%</t>
+          <t>85,74%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -9467,32 +9467,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>133010</t>
+          <t>150484</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>125205</t>
+          <t>141240</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>140082</t>
+          <t>158111</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>79,99%</t>
+          <t>80,55%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>75,29%</t>
+          <t>75,6%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>84,24%</t>
+          <t>84,63%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -9502,32 +9502,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>725564</t>
+          <t>540143</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>675025</t>
+          <t>523555</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>793925</t>
+          <t>557765</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>87,02%</t>
+          <t>82,14%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>80,95%</t>
+          <t>79,62%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>95,21%</t>
+          <t>84,82%</t>
         </is>
       </c>
     </row>
@@ -9545,17 +9545,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>667545</t>
+          <t>470743</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>667545</t>
+          <t>470743</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>667545</t>
+          <t>470743</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -9580,17 +9580,17 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>166292</t>
+          <t>186822</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>166292</t>
+          <t>186822</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>166292</t>
+          <t>186822</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -9615,17 +9615,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>833837</t>
+          <t>657566</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>833837</t>
+          <t>657566</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>833837</t>
+          <t>657566</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -9662,32 +9662,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>160522</t>
+          <t>174357</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>138420</t>
+          <t>150653</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>181935</t>
+          <t>197525</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>15,57%</t>
+          <t>15,46%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>13,43%</t>
+          <t>13,36%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>17,65%</t>
+          <t>17,52%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -9697,32 +9697,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>303124</t>
+          <t>108587</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>119805</t>
+          <t>94506</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>628302</t>
+          <t>123455</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>31,01%</t>
+          <t>12,62%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>12,26%</t>
+          <t>10,98%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>64,27%</t>
+          <t>14,35%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -9732,32 +9732,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>463646</t>
+          <t>282944</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>279901</t>
+          <t>255351</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>906774</t>
+          <t>313412</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>23,08%</t>
+          <t>14,23%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>13,94%</t>
+          <t>12,84%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>45,15%</t>
+          <t>15,76%</t>
         </is>
       </c>
     </row>
@@ -9775,32 +9775,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>870382</t>
+          <t>953171</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>848969</t>
+          <t>930003</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>892484</t>
+          <t>976875</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>84,43%</t>
+          <t>84,54%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>82,35%</t>
+          <t>82,48%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>86,57%</t>
+          <t>86,64%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -9810,32 +9810,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>674436</t>
+          <t>752006</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>349258</t>
+          <t>737138</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>857755</t>
+          <t>766087</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>68,99%</t>
+          <t>87,38%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>35,73%</t>
+          <t>85,65%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>87,74%</t>
+          <t>89,02%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -9845,32 +9845,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>1544818</t>
+          <t>1705177</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1101690</t>
+          <t>1674709</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1728563</t>
+          <t>1732770</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>76,92%</t>
+          <t>85,77%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>54,85%</t>
+          <t>84,24%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>86,06%</t>
+          <t>87,16%</t>
         </is>
       </c>
     </row>
@@ -9888,17 +9888,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>1030904</t>
+          <t>1127528</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>1030904</t>
+          <t>1127528</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>1030904</t>
+          <t>1127528</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -9923,17 +9923,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>977560</t>
+          <t>860593</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>977560</t>
+          <t>860593</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>977560</t>
+          <t>860593</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -9958,17 +9958,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>2008464</t>
+          <t>1988121</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>2008464</t>
+          <t>1988121</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>2008464</t>
+          <t>1988121</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -10005,32 +10005,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>77212</t>
+          <t>84004</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>63948</t>
+          <t>68920</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>93520</t>
+          <t>102393</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>16,33%</t>
+          <t>14,85%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>13,53%</t>
+          <t>12,19%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>19,78%</t>
+          <t>18,1%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -10040,32 +10040,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>170753</t>
+          <t>182542</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>126286</t>
+          <t>163230</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>199600</t>
+          <t>202162</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>20,39%</t>
+          <t>22,05%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>15,08%</t>
+          <t>19,72%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>23,84%</t>
+          <t>24,42%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -10075,32 +10075,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>247966</t>
+          <t>266546</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>205010</t>
+          <t>241525</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>280976</t>
+          <t>292991</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>18,93%</t>
+          <t>19,13%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>15,65%</t>
+          <t>17,33%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>21,45%</t>
+          <t>21,03%</t>
         </is>
       </c>
     </row>
@@ -10118,32 +10118,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>395515</t>
+          <t>481574</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>379207</t>
+          <t>463185</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>408779</t>
+          <t>496658</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>83,67%</t>
+          <t>85,15%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>80,22%</t>
+          <t>81,9%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>86,47%</t>
+          <t>87,81%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -10153,32 +10153,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>666572</t>
+          <t>645228</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>637725</t>
+          <t>625608</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>711039</t>
+          <t>664540</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>79,61%</t>
+          <t>77,95%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>76,16%</t>
+          <t>75,58%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>84,92%</t>
+          <t>80,28%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -10188,32 +10188,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>1062086</t>
+          <t>1126802</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1029076</t>
+          <t>1100357</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1105042</t>
+          <t>1151823</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>81,07%</t>
+          <t>80,87%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>78,55%</t>
+          <t>78,97%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>84,35%</t>
+          <t>82,67%</t>
         </is>
       </c>
     </row>
@@ -10231,17 +10231,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>472727</t>
+          <t>565578</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>472727</t>
+          <t>565578</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>472727</t>
+          <t>565578</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -10266,17 +10266,17 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>837325</t>
+          <t>827770</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>837325</t>
+          <t>827770</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>837325</t>
+          <t>827770</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -10301,17 +10301,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>1310052</t>
+          <t>1393348</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>1310052</t>
+          <t>1393348</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>1310052</t>
+          <t>1393348</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -10333,7 +10333,7 @@
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -10348,32 +10348,32 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>5110</t>
+          <t>5157</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>2051</t>
+          <t>1930</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>11727</t>
+          <t>11622</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>2,12%</t>
+          <t>2,17%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>0,85%</t>
+          <t>0,81%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>4,88%</t>
+          <t>4,9%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -10383,32 +10383,32 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>137208</t>
+          <t>149622</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>122213</t>
+          <t>133210</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>154310</t>
+          <t>168157</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>18,05%</t>
+          <t>17,74%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>16,07%</t>
+          <t>15,8%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>20,3%</t>
+          <t>19,94%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -10418,32 +10418,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>142318</t>
+          <t>154779</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>126122</t>
+          <t>137471</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>162299</t>
+          <t>176015</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>14,22%</t>
+          <t>14,33%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>12,6%</t>
+          <t>12,72%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>16,22%</t>
+          <t>16,29%</t>
         </is>
       </c>
     </row>
@@ -10461,32 +10461,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>235397</t>
+          <t>232071</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>228780</t>
+          <t>225606</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>238456</t>
+          <t>235298</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>97,88%</t>
+          <t>97,83%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>95,12%</t>
+          <t>95,1%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>99,15%</t>
+          <t>99,19%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -10496,32 +10496,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>623086</t>
+          <t>693573</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>605984</t>
+          <t>675038</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>638081</t>
+          <t>709985</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>81,95%</t>
+          <t>82,26%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>79,7%</t>
+          <t>80,06%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>83,93%</t>
+          <t>84,2%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -10531,32 +10531,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>858483</t>
+          <t>925644</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>838502</t>
+          <t>904408</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>874679</t>
+          <t>942952</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>85,78%</t>
+          <t>85,67%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>83,78%</t>
+          <t>83,71%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>87,4%</t>
+          <t>87,28%</t>
         </is>
       </c>
     </row>
@@ -10574,17 +10574,17 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>240507</t>
+          <t>237228</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>240507</t>
+          <t>237228</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>240507</t>
+          <t>237228</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -10609,17 +10609,17 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>760294</t>
+          <t>843195</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>760294</t>
+          <t>843195</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>760294</t>
+          <t>843195</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -10644,17 +10644,17 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>1000801</t>
+          <t>1080423</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>1000801</t>
+          <t>1080423</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>1000801</t>
+          <t>1080423</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -10691,32 +10691,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>457473</t>
+          <t>498544</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>347790</t>
+          <t>460242</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>507987</t>
+          <t>536818</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>13,58%</t>
+          <t>14,52%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>10,33%</t>
+          <t>13,4%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>15,08%</t>
+          <t>15,63%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -10726,32 +10726,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>747393</t>
+          <t>589341</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>561405</t>
+          <t>556022</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>1325870</t>
+          <t>625676</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>20,93%</t>
+          <t>16,24%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>15,72%</t>
+          <t>15,32%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>37,14%</t>
+          <t>17,24%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -10761,32 +10761,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>1204866</t>
+          <t>1087884</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>1010014</t>
+          <t>1037613</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>1880507</t>
+          <t>1142126</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>17,37%</t>
+          <t>15,4%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>14,56%</t>
+          <t>14,69%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>27,1%</t>
+          <t>16,17%</t>
         </is>
       </c>
     </row>
@@ -10804,32 +10804,32 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>2910550</t>
+          <t>2935227</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>2860036</t>
+          <t>2896953</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>3020233</t>
+          <t>2973529</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>86,42%</t>
+          <t>85,48%</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>84,92%</t>
+          <t>84,37%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>89,67%</t>
+          <t>86,6%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -10839,32 +10839,32 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>2822862</t>
+          <t>3039336</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>2244385</t>
+          <t>3003001</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>3008850</t>
+          <t>3072655</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>79,07%</t>
+          <t>83,76%</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>62,86%</t>
+          <t>82,76%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>84,28%</t>
+          <t>84,68%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -10874,32 +10874,32 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>5733412</t>
+          <t>5974564</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>5057771</t>
+          <t>5920322</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>5928264</t>
+          <t>6024835</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t>82,63%</t>
+          <t>84,6%</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>72,9%</t>
+          <t>83,83%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>85,44%</t>
+          <t>85,31%</t>
         </is>
       </c>
     </row>
@@ -10917,17 +10917,17 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>3368023</t>
+          <t>3433771</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>3368023</t>
+          <t>3433771</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>3368023</t>
+          <t>3433771</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -10952,17 +10952,17 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>3570255</t>
+          <t>3628677</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>3570255</t>
+          <t>3628677</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>3570255</t>
+          <t>3628677</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -10987,17 +10987,17 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>6938278</t>
+          <t>7062448</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>6938278</t>
+          <t>7062448</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>6938278</t>
+          <t>7062448</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
